--- a/important_mails_2026-08-01.xlsx
+++ b/important_mails_2026-08-01.xlsx
@@ -2870,7 +2870,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>付款/资金类</t>
+          <t>产品链接/合规类</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2885,74 +2885,22 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Sat, 25 Jul 2026 13:57:00 +0000</t>
+          <t>Wed, 29 Jul 2026 09:26:45 +0000</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>"toys-safety-mv@amazon.de" &lt;toys-safety-mv@amazon.de&gt;</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Your payment is on the way</t>
+          <t>RE:[CASE 13104358872] SELLER: A1UYGOR4ZW45MU, ASIN: B0F13M1H6F,
+ MARKETPLACE: 4 - PS - APPEAL</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulations! Your payment is on the way and will arrive soon.
- Disbursement Attempted
-Congratulations Weihai EU! Your payment is on the way and will arrive within three to five days.
-On 07/25/26 13:56 CEST, we initiated a transfer to your payment method (bank account ending in 229) in the amount of €
- 297.14.
- If the amount is less than expected, here are a few questions to consider:
- Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims, or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
- Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees, and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
-To learn more about Payment Reports in Seller Central, please visit our official course.
-We wish you continued success!
-Thank you for selling in the Amazon store,
-Amazon Services
-Help us improve your payment experience on Ama</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 29 Jul 2026 09:26:45 +0000</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>"toys-safety-mv@amazon.de" &lt;toys-safety-mv@amazon.de&gt;</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>RE:[CASE 13104358872] SELLER: A1UYGOR4ZW45MU, ASIN: B0F13M1H6F,
- MARKETPLACE: 4 - PS - APPEAL</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 13104358872] SELLER: A1UYGOR4ZW45MU, ASIN: B0F13M1H6F, MARKETPLACE: 4 - PS - APPEAL
@@ -2977,39 +2925,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Fri, 31 Jul 2026 23:32:42 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -3025,40 +2973,40 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Fri, 31 Jul 2026 23:27:07 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -3074,39 +3022,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Fri, 31 Jul 2026 07:22:18 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3125,39 +3073,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Fri, 31 Jul 2026 07:18:49 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 145 PCS Eisenbahn Elektrisch Cube Track, 3D Schwerkrafttrotzendes Zug Set, DIY Zugstrecken Spielzeug, STEM Lernspielzeug &amp;amp; Geschenkidee für Kinder 3–8 Jahre, Kreatives Bauen Spielzeug
@@ -3179,40 +3127,40 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Jul 2026 04:16:04 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Notificaciones de Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Soluciona los errores de precio para restablecer los listings
  desactivados.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Eliminar errores de precio
@@ -3233,39 +3181,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Jul 2026 04:16:02 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Powiadomienia Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Rozwiąż błędy w obrębie cen, aby umożliwić ponowną aktywację ofert</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
  Zatrzymanie spowodowane błędem ceny
@@ -3286,39 +3234,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Jul 2026 16:57:33 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>"Amazon.pl" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Informacje o Twoim koncie bankowym Amazon zostały pomyślnie zaktualizowane</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
  Informacje o Twoim koncie bankowym Amazon zostały pomyślnie zaktualizowane
@@ -3331,39 +3279,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Jul 2026 16:47:43 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>"Amazon.es" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>La información de tu cuenta bancaria de Amazon se ha actualizado correctamente</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
  La información de tu cuenta bancaria de Amazon se ha actualizado correctamente
@@ -3376,39 +3324,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Jul 2026 16:45:55 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>"Amazon.es" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>La información de tu cuenta bancaria de Amazon se ha actualizado correctamente</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
  La información de tu cuenta bancaria de Amazon se ha actualizado correctamente
@@ -3421,39 +3369,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Jul 2026 11:26:20 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Ukończ rejestrację opakowań UE według kraju</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>Ukończ rejestrację opakowań UE według kraju
  96
@@ -3463,39 +3411,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Jul 2026 17:52:28 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Presentar información de cumplimiento normativo de la RAP en Portugal</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
  La normativa portuguesa sobre la RAP se aplica a los productos vendidos a clientes de Portugal.
@@ -3512,39 +3460,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Jul 2026 14:32:02 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Add WhatsApp to your notification preferences</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
  Stay connected with account updates on WhatsApp—opt in today to get started
@@ -3561,39 +3509,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Jul 2026 04:57:25 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3609,39 +3557,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Jul 2026 05:07:54 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3657,39 +3605,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Jul 2026 16:10:45 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Your Amazon bank account information has been updated successfully</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
  Your Amazon bank account information has been updated successfully
@@ -3705,39 +3653,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Jul 2026 10:35:17 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Zx1U3/hDuM)</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3757,39 +3705,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Jul 2026 05:01:14 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3805,39 +3753,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Jul 2026 05:03:32 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3853,39 +3801,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Jul 2026 09:30:25 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3901,39 +3849,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Jul 2026 04:57:37 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3949,39 +3897,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Jul 2026 14:04:25 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -4002,39 +3950,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Jul 2026 04:59:54 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4050,39 +3998,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Jul 2026 14:58:02 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -4103,39 +4051,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Fri, 17 Jul 2026 05:03:59 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4151,39 +4099,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Thu, 16 Jul 2026 05:02:32 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4199,39 +4147,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Wed, 15 Jul 2026 04:56:43 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4247,39 +4195,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Jul 2026 15:08:13 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -4300,39 +4248,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Tue, 14 Jul 2026 04:45:43 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4348,39 +4296,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Sun, 12 Jul 2026 14:23:23 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $88.37 in an attempt to settle your Amazon seller account balance.
@@ -4396,39 +4344,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 09:58:04 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4444,39 +4392,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 05:37:52 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4492,39 +4440,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 05:20:26 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4540,39 +4488,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Thu, 9 Jul 2026 03:39:42 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4588,39 +4536,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Jul 2026 05:28:59 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (0uWEj59btv)</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4640,39 +4588,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Jul 2026 04:32:11 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4688,39 +4636,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Jul 2026 09:21:14 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4736,39 +4684,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 09:24:36 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4784,39 +4732,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Jul 2026 04:17:03 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (go0BbIMUoR)</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4836,39 +4784,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Jul 2026 16:27:45 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (hbXn1jQJTV)</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4893,40 +4841,40 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Jul 2026 11:09:39 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Verstrek KYC-verificatie binnen 45 dagen om beperkingen te
  voorkomen</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
  Verstrek KYC-verificatie binnen 45 dagen om beperkingen te voorkomen
@@ -4945,39 +4893,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Jul 2026 10:52:41 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Provide KYC verification within 45 days to avoid restrictions</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>96
  Provide KYC verification within 45 days to avoid restrictions
@@ -4996,39 +4944,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Jul 2026 09:42:14 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Provide KYC verification within 45 days to avoid restrictions</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>96
  Provide KYC verification within 45 days to avoid restrictions
@@ -5047,39 +4995,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Fri, 24 Jul 2026 09:24:08 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Fournissez une vérification KYC sous 45 jours pour éviter les restrictions</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Fournissez une vérification KYC sous 45 jours pour éviter les restrictions
@@ -5095,39 +5043,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Jul 2026 08:07:04 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Know Your Customer (KYC) verification process support</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
  Pending Know Your Customer (KYC) account verification
@@ -5144,39 +5092,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Jul 2026 07:52:22 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>"seller-verification-review-cn@amazon.co.uk" &lt;seller-verification-review-cn@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>[需要采取的操作] 需要您的“我要开店”付款账户的相关信息</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>96
 [需要采取的操作] 需要您的“我要开店”付款账户的相关信息
@@ -5214,39 +5162,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Jul 2026 08:31:05 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Know Your Customer (KYC) verification process support</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>96
  Pending Know Your Customer (KYC) account verification
@@ -5263,39 +5211,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Jul 2026 08:30:30 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>"seller-verification-review-cn@amazon.co.uk" &lt;seller-verification-review-cn@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>[需要采取的操作] 需要您的“我要开店”付款账户的相关信息</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>96
 [需要采取的操作] 需要您的“我要开店”付款账户的相关信息
@@ -5333,39 +5281,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Jul 2026 16:00:40 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Know Your Customer (KYC) verification process support</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>96
  Pending Know Your Customer (KYC) account verification
@@ -5382,39 +5330,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Jul 2026 15:59:18 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>"seller-verification-review-cn@amazon.co.uk" &lt;seller-verification-review-cn@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>[需要采取的操作] 需要您的“我要开店”付款账户的相关信息</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>96
 [需要采取的操作] 需要您的“我要开店”付款账户的相关信息
@@ -5452,39 +5400,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Jul 2026 07:44:38 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Know Your Customer (KYC) verification process support</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>96
  Pending Know Your Customer (KYC) account verification
@@ -5501,40 +5449,40 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Sun, 19 Jul 2026 07:43:19 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>"seller-verification-review-cn@amazon.co.uk" &lt;seller-verification-review-cn@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Information needed for your Selling on Amazon
  payment account</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>96
 [Action Required] Information needed for your Selling on Amazon payment account
@@ -5549,39 +5497,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Mon, 13 Jul 2026 06:09:58 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>【官方提示】请尽快通过您的欧洲站卖家资质KYC审核，以保证正常销售</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">账户注册
 															资质审查
@@ -5614,39 +5562,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 08:27:01 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Know Your Customer (KYC) verification process support</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>96
  Pending Know Your Customer (KYC) account verification
@@ -5663,40 +5611,40 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Sat, 11 Jul 2026 08:25:53 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>"seller-verification-review-cn@amazon.co.uk" &lt;seller-verification-review-cn@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Information needed for your Selling on Amazon
  payment account</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>96
 [Action Required] Information needed for your Selling on Amazon payment account
@@ -5711,39 +5659,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Fri, 10 Jul 2026 11:11:12 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Know Your Customer (KYC) verification process support</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>96
  Pending Know Your Customer (KYC) account verification
@@ -5757,6 +5705,58 @@
  We’re here to help.
  If you have any questions, you can contact us at any time via Amazon Selling Partner Support .
  For more informa</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 25 Jul 2026 13:57:00 +0000</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Your payment is on the way</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulations! Your payment is on the way and will arrive soon.
+ Disbursement Attempted
+Congratulations Weihai EU! Your payment is on the way and will arrive within three to five days.
+On 07/25/26 13:56 CEST, we initiated a transfer to your payment method (bank account ending in 229) in the amount of €
+ 297.14.
+ If the amount is less than expected, here are a few questions to consider:
+ Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims, or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
+ Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees, and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
+To learn more about Payment Reports in Seller Central, please visit our official course.
+We wish you continued success!
+Thank you for selling in the Amazon store,
+Amazon Services
+Help us improve your payment experience on Ama</t>
         </is>
       </c>
     </row>
